--- a/光伏配储项目/电价数据/2026/泥乔站.xlsx
+++ b/光伏配储项目/电价数据/2026/泥乔站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50989</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.71988</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5646</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.51546</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45298</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44761</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42341</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26778</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21347</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07653</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06284000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05084</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03133</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03895000000000001</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04417</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.00697</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.0193</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08617</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01437</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00222</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00352</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14521</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21297</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23614</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21302</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11412</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00574</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00701</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.15375</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.21228</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.18971</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22261</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.18058</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12179</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19293</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.26049</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.01346</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.23061</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.02071</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.44882</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43712</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5262100000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.47994</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.75915</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61446</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.5080899999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.50315</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.11521</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5834199999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.54006</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.25347</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50129</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6120399999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.56825</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43217</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48408</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41872</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4285</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62152</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.42617</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75537</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.16776</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8712799999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54525</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5274099999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5145700000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.51075</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47712</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42524</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5275700000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65323</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7503500000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44245</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44594</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08677</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04877</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26155</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26808</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.25343</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.58729</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.18871</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27547</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.26582</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.57901</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.02258</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26832</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.22788</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15729</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23077</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.25509</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.25588</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.43552</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42127</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.26085</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.46343</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.27492</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.7073200000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.9248</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.87915</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.26015</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.84378</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.41857</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.81878</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43808</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5980800000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43914</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43379</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40778</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.34556</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5442400000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47373</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.41703</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39691</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.42516</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47401</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44289</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40532</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28501</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.16262</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.46971</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.4387799999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.45565</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.26579</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.06770999999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21373</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.14456</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20298</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19046</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24704</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27969</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.28295</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.24246</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.20834</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.03518</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.47474</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.03424</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.28249</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34405</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.30329</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47839</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28437</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26318</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26387</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19318</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10792</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11066</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08083</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.25123</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21319</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.12835</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28804</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44665</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.20997</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04809</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17699</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.01355</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21332</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.00266</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.02961</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.04653</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07615000000000001</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.20512</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.16809</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20456</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.15347</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19808</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14345</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.20218</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.2289</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25664</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28561</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.4709</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25694</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.2921</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27444</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27725</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04516</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04024</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04359</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04611999999999999</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04708</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.0478</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04629</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04661999999999999</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04747</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04667</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04568</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04785</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04636999999999999</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04781000000000001</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04903</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04865</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04636</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04728</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22004</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04904</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05178</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00215</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14705</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03753</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09884</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41732</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35133</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6643600000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44656</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04262</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04592</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04514</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04186</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03233</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04072</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10692</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00104</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03742</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04689</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04115</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04132</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04123</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04113</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04054</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04332</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04039</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03902000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04406</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04112</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.0422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04267</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04309</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04646</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04606</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2023</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14477</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29628</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33771</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32281</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2835299999999999</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29361</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28373</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27348</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27362</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17432</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16058</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17321</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14956</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16128</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16066</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23954</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21608</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22868</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27195</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28373</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27077</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28315</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.43183</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.48321</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.61383</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.47048</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4655899999999999</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15729</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7910900000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9200199999999999</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49429</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92776</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31898</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.92911</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6386499999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22797</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88903</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.57977</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37278</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0617</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.57286</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.82673</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.8089299999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.80604</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.88119</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.89264</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.52673</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43146</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44301</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48827</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25011</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8800399999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55176</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6646299999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5489700000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46106</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42931</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.4447</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45198</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45325</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42233</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41532</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43437</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41352</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45132</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58963</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59684</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60197</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.64549</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45456</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.45258</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.6654500000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44733</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86488</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.8889</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.93298</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.9170199999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.89425</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43414</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.45778</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.48947</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27319</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3533</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02304</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.49884</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.49883</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.61581</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6898500000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.44813</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.50836</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.44618</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50064</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28911</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16472</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26107</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20115</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27748</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.54316</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27588</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.25043</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27497</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24753</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44706</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5976699999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88976</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35712</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13679</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7115499999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8055</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65134</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59073</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45103</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50043</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50092</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39633</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43443</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.92338</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43026</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.41562</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.19145</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.73548</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.02211</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.05607</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23695</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.67679</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.88182</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26841</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.52349</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38634</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48383</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.42995</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.6064400000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46566</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.68635</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46667</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43955</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42556</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38813</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32649</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42567</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.40375</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.14755</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23712</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14642</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14909</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15604</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14478</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14226</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14481</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25887</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14543</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26857</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26871</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14328</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05196</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11476</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14746</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14249</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14773</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38259</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45138</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39362</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43801</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44121</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44616</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44543</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40422</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35066</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.6134700000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39032</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47032</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41742</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.5892500000000001</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.22477</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.41028</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.40761</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44396</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45642</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24897</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42357</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.50742</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36063</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28399</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.42638</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.28897</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03403</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25366</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.20832</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07443000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.1834</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24479</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28607</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27034</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25239</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27361</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42631</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50295</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7734099999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.44686</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46513</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.4305</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30956</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.44237</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.46011</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34965</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.45851</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.72758</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41467</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38211</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42958</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40741</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6496000000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.87454</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48658</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.48215</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34507</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26139</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13609</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19525</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24625</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27856</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.02504</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13014</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.01669</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23729</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24761</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.01032</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14497</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.02548</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23287</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23592</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40837</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63163</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6019600000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.57624</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46226</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.5898300000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47759</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.72322</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45344</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.4598</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40199</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48157</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43058</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49328</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46594</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45688</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42146</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40742</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41974</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41147</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45081</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5612999999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50092</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45096</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41326</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42727</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.42022</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.44873</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.43305</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.15162</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.03918</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03097</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.51162</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.9916200000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.17698</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.10556</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.00464</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26804</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.03334</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48594</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43196</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5084</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.42687</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.57523</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.65835</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.6405700000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.61468</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.67872</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.50513</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.49593</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7446200000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.6904400000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.56513</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.60645</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.40251</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46313</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.46022</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45352</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50735</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41448</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43147</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44457</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42638</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44262</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41006</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44578</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39446</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15784</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27109</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03662</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45321</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46417</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01567</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18515</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.39513</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36282</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44375</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.46421</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.4832</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24715</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23529</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23699</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24541</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25167</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03667</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05299</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17475</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.03632</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14834</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15244</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.05653</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.00563</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.26413</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.46573</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.42817</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35413</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19499</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.18744</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13253</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01611</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00155</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.0436</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04153</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.01565</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.07858</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.14095</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27679</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22462</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22532</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22613</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.23041</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.24092</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26752</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.25049</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24402</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23507</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.25127</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25493</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.2379</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24455</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.26186</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24991</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26365</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.27746</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27782</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.26029</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.22045</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.2402</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21855</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18913</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.09096</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.03202</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.03854999999999999</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.16201</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.16026</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.03169</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23593</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21945</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.20416</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16883</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16028</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13617</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.16045</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.19093</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.11343</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12796</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.19318</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.16412</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.1864</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.17372</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.22406</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.17416</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.22457</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.23118</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.21275</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21915</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.13453</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.03668</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.44971</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.20813</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.00392</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.17395</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16963</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.01598</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.03993</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.01891</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18837</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26793</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.02912</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.08456999999999999</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04978</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.04129</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.04836</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.01745</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.04107</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23395</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28014</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25163</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.2809700000000001</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.18878</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3262</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10579</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.26337</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25396</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25093</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.11541</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24058</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45458</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.17939</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25574</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26981</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.18753</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14359</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10292</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33208</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.24232</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26549</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.62675</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.62238</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27205</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26566</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.16678</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26029</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.2662</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26504</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26237</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24569</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28042</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.42561</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.41263</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.46873</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.48329</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.50057</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.61021</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.60534</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.03262</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.39315</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.43123</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46822</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.54111</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47365</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45176</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43087</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.8538600000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.49548</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42694</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.44869</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36902</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4671</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.45254</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.20415</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17442</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23341</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.25898</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19161</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26258</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27327</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.46594</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46493</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.55955</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5608</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46164</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.55136</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46388</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49638</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39714</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53225</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52011</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.70531</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.75039</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54936</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55198</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44477</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37677</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29237</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27383</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26535</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25804</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.2512</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.24039</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23897</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25607</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.19183</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.12916</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.01226</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16882</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01091</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.11711</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.00412</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.01887</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01596</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02344</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.03212</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23505</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03139</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01694</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02857</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.10599</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06154</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11961</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13491</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16251</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22412</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18161</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.18119</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20898</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.25256</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40417</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38045</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.7435</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27831</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27253</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26151</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23372</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22712</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.1962</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19622</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.20056</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21782</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11262</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01308</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01254</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03623</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.08051</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.05403</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00399</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01337</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04455</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02386</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02393</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.03111</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.23378</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04801</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.19297</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.18694</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.14469</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.2044</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.15124</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.19717</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22236</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18608</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.24056</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.26657</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.52763</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41333</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38653</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38601</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.51234</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41749</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27388</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23433</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.19004</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17473</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11438</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17781</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.16567</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08946</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10679</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.07209</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03549</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03633</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03687</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03549</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04567</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05275</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06042</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03551</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07318999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11685</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08791</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16706</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14812</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.09101999999999999</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04639</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21635</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09814000000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.09284999999999999</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18927</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.14216</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.17022</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14881</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.1837</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.20294</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.20392</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21679</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25645</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.26045</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26205</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41286</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4968399999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41795</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41489</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41422</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38236</v>
       </c>
     </row>
   </sheetData>
